--- a/pixy2.xlsx
+++ b/pixy2.xlsx
@@ -5,16 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/likayauelwin/Documents/GitHub/2025-WRO-Future-Engineer/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/likayauelwin/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479A67CD-FA4F-0C42-9C7F-95D7C2EA5D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EB6B9B-85A6-9F47-BCD2-F1477DA0B1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="17240" xr2:uid="{50C2FC8F-A61D-EA40-BD48-FD46821D1210}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{50C2FC8F-A61D-EA40-BD48-FD46821D1210}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$D$18:$D$30</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$F$18:$F$30</definedName>
+    <definedName name="_xlchart.v2.2" hidden="1">Sheet1!$D$18:$D$30</definedName>
+    <definedName name="_xlchart.v2.3" hidden="1">Sheet1!$F$18:$F$30</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>Area</t>
   </si>
@@ -64,12 +70,15 @@
   <si>
     <t>Block at right (green) case:</t>
   </si>
+  <si>
+    <t xml:space="preserve"> dist (cm)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -82,6 +91,13 @@
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Aptos Narrow"/>
+      <family val="3"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -212,382 +228,8 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.15023234697500207"/>
-                  <c:y val="1.6305315011360774E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$D$2:$D$9</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>34</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$E$2:$E$9</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>107</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>87</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>62</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>39</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>22</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-609E-1549-96A2-B39C37C25EA4}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="395604576"/>
-        <c:axId val="395470176"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="395604576"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="395470176"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="395470176"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="395604576"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
               <c:layout>
@@ -628,54 +270,96 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$D$18:$D$23</c:f>
+              <c:f>Sheet1!$D$18:$D$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>6</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>23</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>40</c:v>
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>67</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$18:$E$23</c:f>
+              <c:f>Sheet1!$E$18:$E$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>215</c:v>
+                  <c:v>211</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>224</c:v>
+                  <c:v>217</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>233</c:v>
+                  <c:v>225</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>231</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>237</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>245</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>265</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>284</c:v>
+                <c:pt idx="6">
+                  <c:v>248</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>255</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>259</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>261</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>266</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>277</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -867,7 +551,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -1191,6 +875,1224 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.4932852143482062E-2"/>
+                  <c:y val="6.6221201516477105E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>55</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>35</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-044A-D84C-BF4C-61589A1A7EAD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1902293088"/>
+        <c:axId val="1902296192"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1902293088"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1902296192"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1902296192"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1902293088"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.20210428113045656"/>
+                  <c:y val="7.4342959117456114E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>55</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$2:$F$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AE38-EF49-9F2F-71983300E86B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="251846336"/>
+        <c:axId val="251836752"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="251846336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="251836752"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="251836752"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="251846336"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.14770656172537036"/>
+                  <c:y val="4.5504723869053694E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$18:$D$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>67</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$18:$F$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>54.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>38.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>37.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>34.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>28</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B668-D54A-9492-A2D6E4735669}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1898060400"/>
+        <c:axId val="1898273184"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1898060400"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1898273184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1898273184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1898060400"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1311,6 +2213,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2859,44 +3841,1040 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>596900</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>215900</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>101601</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9ACD1491-7B76-61A3-2C66-500D9C7276E2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
@@ -2927,54 +4905,10 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>160867</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>287866</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>135570</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84CFBE71-5D11-1DC9-C9F8-E27B765324FC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13106400" y="973667"/>
-          <a:ext cx="7831666" cy="5054703"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -3007,7 +4941,115 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>479778</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>158045</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>107244</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>56445</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{456B5637-DB1B-5EF1-90FE-7E8235B95E06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>474983</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>37879</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>96534</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>139479</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C304B611-DF6F-83B8-F6FD-1556E77DB1AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>488951</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>124354</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>94193</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EB175EB-0B59-A452-F15E-5735C015D9F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3334,13 +5376,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4ABAF86-B548-3B4C-9384-3449F00EA32C}">
   <dimension ref="C1:G41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="28.83203125" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" customWidth="1"/>
     <col min="5" max="5" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="3:6" x14ac:dyDescent="0.2">
       <c r="C1" t="s">
         <v>7</v>
       </c>
@@ -3350,126 +5392,303 @@
       <c r="E1" t="s">
         <v>1</v>
       </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="3:6" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>107</v>
+        <v>114</v>
+      </c>
+      <c r="F2">
+        <v>66</v>
       </c>
     </row>
-    <row r="3" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>99</v>
+      </c>
+      <c r="F3">
+        <v>56</v>
       </c>
     </row>
-    <row r="4" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>87</v>
+        <v>94</v>
+      </c>
+      <c r="F4">
+        <v>51</v>
       </c>
     </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D5">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>62</v>
+        <v>90</v>
+      </c>
+      <c r="F5">
+        <v>46</v>
       </c>
     </row>
-    <row r="6" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D6">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E6">
+        <v>85</v>
+      </c>
+      <c r="F6">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D7">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E7">
+        <v>82</v>
+      </c>
+      <c r="F7">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>71</v>
+      </c>
+      <c r="F8">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D9">
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>60</v>
+      </c>
+      <c r="F9">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D10">
         <v>39</v>
       </c>
+      <c r="E10">
+        <v>50</v>
+      </c>
+      <c r="F10">
+        <v>27.5</v>
+      </c>
     </row>
-    <row r="8" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="D8">
-        <v>34</v>
-      </c>
-      <c r="E8">
+    <row r="11" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D11">
+        <v>44</v>
+      </c>
+      <c r="E11">
+        <v>46</v>
+      </c>
+      <c r="F11">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="12" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D12">
+        <v>50</v>
+      </c>
+      <c r="E12">
+        <v>40</v>
+      </c>
+      <c r="F12">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="13" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D13">
+        <v>55</v>
+      </c>
+      <c r="E13">
+        <v>35</v>
+      </c>
+      <c r="F13">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C17" t="s">
-        <v>8</v>
-      </c>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D17" t="s">
         <v>0</v>
       </c>
       <c r="E17" t="s">
         <v>1</v>
       </c>
+      <c r="F17" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:6" x14ac:dyDescent="0.2">
       <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18">
+        <v>211</v>
+      </c>
+      <c r="F18">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C19" t="s">
         <v>2</v>
       </c>
-      <c r="D18">
-        <v>6</v>
-      </c>
-      <c r="E18">
-        <v>215</v>
+      <c r="D19">
+        <v>12</v>
+      </c>
+      <c r="E19">
+        <v>217</v>
+      </c>
+      <c r="F19">
+        <v>54.5</v>
       </c>
     </row>
-    <row r="19" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="D19">
-        <v>7</v>
-      </c>
-      <c r="E19">
-        <v>224</v>
+    <row r="20" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D20">
+        <v>16</v>
+      </c>
+      <c r="E20">
+        <v>225</v>
+      </c>
+      <c r="F20">
+        <v>49</v>
       </c>
     </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="D20">
-        <v>11</v>
-      </c>
-      <c r="E20">
-        <v>233</v>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D21">
+        <v>20</v>
+      </c>
+      <c r="E21">
+        <v>231</v>
+      </c>
+      <c r="F21">
+        <v>47</v>
       </c>
     </row>
-    <row r="21" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="D21">
-        <v>15</v>
-      </c>
-      <c r="E21">
+    <row r="22" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D22">
+        <v>25</v>
+      </c>
+      <c r="E22">
+        <v>237</v>
+      </c>
+      <c r="F22">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D23">
+        <v>31</v>
+      </c>
+      <c r="E23">
         <v>245</v>
       </c>
+      <c r="F23">
+        <v>38.5</v>
+      </c>
     </row>
-    <row r="22" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="D22">
-        <v>23</v>
-      </c>
-      <c r="E22">
-        <v>265</v>
+    <row r="24" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D24">
+        <v>34</v>
+      </c>
+      <c r="E24">
+        <v>248</v>
+      </c>
+      <c r="F24">
+        <v>37.5</v>
       </c>
     </row>
-    <row r="23" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="D23">
-        <v>40</v>
-      </c>
-      <c r="E23">
-        <v>284</v>
+    <row r="25" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D25">
+        <v>41</v>
+      </c>
+      <c r="E25">
+        <v>255</v>
+      </c>
+      <c r="F25">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="26" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D26">
+        <v>45</v>
+      </c>
+      <c r="E26">
+        <v>259</v>
+      </c>
+      <c r="F26">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D27">
+        <v>50</v>
+      </c>
+      <c r="E27">
+        <v>261</v>
+      </c>
+      <c r="F27">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D28">
+        <v>55</v>
+      </c>
+      <c r="E28">
+        <v>266</v>
+      </c>
+      <c r="F28">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D29">
+        <v>60</v>
+      </c>
+      <c r="E29">
+        <v>272</v>
+      </c>
+      <c r="F29">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="D30">
+        <v>67</v>
+      </c>
+      <c r="E30">
+        <v>277</v>
+      </c>
+      <c r="F30">
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="4:7" x14ac:dyDescent="0.2">
@@ -3546,6 +5765,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/pixy2.xlsx
+++ b/pixy2.xlsx
@@ -5,22 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/likayauelwin/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/likayauelwin/Documents/GitHub/2025-WRO-Future-Engineer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EB6B9B-85A6-9F47-BCD2-F1477DA0B1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06794D3B-C090-564B-AE3C-402AB0C8108B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{50C2FC8F-A61D-EA40-BD48-FD46821D1210}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$D$18:$D$30</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$F$18:$F$30</definedName>
-    <definedName name="_xlchart.v2.2" hidden="1">Sheet1!$D$18:$D$30</definedName>
-    <definedName name="_xlchart.v2.3" hidden="1">Sheet1!$F$18:$F$30</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -228,14 +222,15 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="log"/>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.28359266286057061"/>
-                  <c:y val="0.18714604513110214"/>
+                  <c:x val="-9.5920319807452414E-2"/>
+                  <c:y val="0.31945950434712173"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -275,43 +270,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>31</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>34</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>41</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>45</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>50</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>55</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>60</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>67</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -323,43 +318,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>211</c:v>
+                  <c:v>195</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>217</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>225</c:v>
-                </c:pt>
                 <c:pt idx="3">
+                  <c:v>226</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>231</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>237</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>245</c:v>
+                  <c:v>235</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>248</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>255</c:v>
+                  <c:v>247</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>259</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>261</c:v>
+                  <c:v>260</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>266</c:v>
+                  <c:v>265</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>272</c:v>
+                  <c:v>269</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>277</c:v>
+                  <c:v>280</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -962,7 +957,8 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="log"/>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
@@ -1008,41 +1004,32 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
-                <c:pt idx="0">
+                <c:pt idx="3">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>14</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>16</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>18</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>22</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>32</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>39</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>44</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>50</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>55</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1053,41 +1040,32 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>114</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>94</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>90</c:v>
+                  <c:v>110</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>85</c:v>
+                  <c:v>106</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>82</c:v>
+                  <c:v>96</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>71</c:v>
+                  <c:v>88</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>60</c:v>
+                  <c:v>78</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>50</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>40</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>35</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1366,7 +1344,7 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="log"/>
+            <c:trendlineType val="power"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
@@ -1412,41 +1390,32 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
-                <c:pt idx="0">
+                <c:pt idx="3">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>14</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>16</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>18</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>22</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>32</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>39</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>44</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>50</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>55</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1457,41 +1426,32 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>66</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>51</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>46</c:v>
+                  <c:v>74.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>43</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>39.5</c:v>
+                  <c:v>54.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>35.5</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>30.5</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>27.5</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>25.5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>23.5</c:v>
-                </c:pt>
                 <c:pt idx="11">
-                  <c:v>22</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1770,7 +1730,7 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="log"/>
+            <c:trendlineType val="power"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
@@ -1817,43 +1777,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>31</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>34</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>41</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>45</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>50</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>55</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>60</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>67</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1865,43 +1825,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>60</c:v>
+                  <c:v>73.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>54.5</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>49</c:v>
+                  <c:v>49.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>47</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38.5</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>37.5</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>34.5</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>33.5</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>32</c:v>
+                  <c:v>29.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>31</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>30.5</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>28</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5400,135 +5360,104 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>114</v>
-      </c>
-      <c r="F2">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="D3">
-        <v>9</v>
-      </c>
-      <c r="E3">
-        <v>99</v>
-      </c>
-      <c r="F3">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="D4">
-        <v>11</v>
-      </c>
-      <c r="E4">
-        <v>94</v>
-      </c>
-      <c r="F4">
-        <v>51</v>
-      </c>
     </row>
     <row r="5" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D5">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="F5">
-        <v>46</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="6" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D6">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="F6">
-        <v>43</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D7">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F7">
-        <v>39.5</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="8" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D8">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E8">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="F8">
-        <v>35.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D9">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E9">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="F9">
-        <v>30.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D10">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E10">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F10">
-        <v>27.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D11">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E11">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="F11">
-        <v>25.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D12">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E12">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F12">
-        <v>23.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="13" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D13">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E13">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="3:6" x14ac:dyDescent="0.2">
@@ -5547,13 +5476,13 @@
         <v>8</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E18">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="F18">
-        <v>60</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.2">
@@ -5564,40 +5493,40 @@
         <v>12</v>
       </c>
       <c r="E19">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F19">
-        <v>54.5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D20">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E20">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="F20">
-        <v>49</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F21">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D22">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E22">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="F22">
         <v>42</v>
@@ -5605,90 +5534,90 @@
     </row>
     <row r="23" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D23">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E23">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="F23">
-        <v>38.5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D24">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E24">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="F24">
-        <v>37.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D25">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E25">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="F25">
-        <v>34.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E26">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F26">
-        <v>33.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D27">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E27">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F27">
-        <v>32</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="28" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D28">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E28">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F28">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D29">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F29">
-        <v>30.5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D30">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E30">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F30">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="4:7" x14ac:dyDescent="0.2">

--- a/pixy2.xlsx
+++ b/pixy2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/likayauelwin/Documents/GitHub/2025-WRO-Future-Engineer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06794D3B-C090-564B-AE3C-402AB0C8108B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C1C006-B70A-4040-B0BC-4F10D7A196FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{50C2FC8F-A61D-EA40-BD48-FD46821D1210}"/>
+    <workbookView xWindow="-640" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{50C2FC8F-A61D-EA40-BD48-FD46821D1210}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -270,7 +270,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>7</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>12</c:v>
@@ -279,34 +279,34 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>19</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>22</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>26</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>30</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>36</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>40</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>48</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>53</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>59</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>69</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -318,43 +318,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>195</c:v>
+                  <c:v>187</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>212</c:v>
+                  <c:v>205</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>217</c:v>
+                  <c:v>211</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>226</c:v>
+                  <c:v>214</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>231</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>235</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>240</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>247</c:v>
+                  <c:v>237</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>252</c:v>
+                  <c:v>244</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>260</c:v>
+                  <c:v>253</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>257</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>265</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>269</c:v>
-                </c:pt>
                 <c:pt idx="12">
-                  <c:v>280</c:v>
+                  <c:v>271</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1730,17 +1730,18 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="power"/>
+            <c:trendlineType val="poly"/>
+            <c:order val="6"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.14770656172537036"/>
-                  <c:y val="4.5504723869053694E-2"/>
+                  <c:x val="8.9025074665838339E-2"/>
+                  <c:y val="9.412831279064518E-2"/>
                 </c:manualLayout>
               </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:numFmt formatCode="#,##0.000000000" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
                 <a:ln>
@@ -1777,7 +1778,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>7</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>12</c:v>
@@ -1786,34 +1787,34 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>19</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>22</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>26</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>30</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>36</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>40</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>48</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>53</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>59</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>69</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1825,16 +1826,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>73.5</c:v>
+                  <c:v>74.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>49.5</c:v>
+                  <c:v>48.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>44</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>42</c:v>
@@ -1846,22 +1847,22 @@
                   <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>34</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>31</c:v>
+                  <c:v>29.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>29.5</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>27</c:v>
+                  <c:v>25.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>26</c:v>
+                  <c:v>23.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>24</c:v>
+                  <c:v>21.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1943,7 +1944,7 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1898273184"/>
-        <c:crosses val="autoZero"/>
+        <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
@@ -5476,13 +5477,13 @@
         <v>8</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F18">
-        <v>73.5</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.2">
@@ -5493,10 +5494,10 @@
         <v>12</v>
       </c>
       <c r="E19">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="F19">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.2">
@@ -5504,29 +5505,29 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="F20">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D21">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E21">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F21">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D22">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E22">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="F22">
         <v>42</v>
@@ -5534,10 +5535,10 @@
     </row>
     <row r="23" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D23">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E23">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="F23">
         <v>39</v>
@@ -5545,10 +5546,10 @@
     </row>
     <row r="24" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D24">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E24">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="F24">
         <v>36</v>
@@ -5556,68 +5557,68 @@
     </row>
     <row r="25" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D25">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E25">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="F25">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D26">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E26">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="F26">
-        <v>31</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="27" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D27">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E27">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="F27">
-        <v>29.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D28">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E28">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="F28">
-        <v>27</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="29" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D29">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E29">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F29">
-        <v>26</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="30" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D30">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E30">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="F30">
-        <v>24</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="34" spans="4:7" x14ac:dyDescent="0.2">
